--- a/用卷/2024.xlsx
+++ b/用卷/2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0170BD6-BF08-4A31-A391-31A7E52072DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074D2BC8-B96C-475E-A1F1-AC44A57F68AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="96">
   <si>
     <t>年份</t>
   </si>
@@ -275,12 +275,6 @@
   </si>
   <si>
     <t>英语听力2次机会,较高分数计入总成绩,均使用PETS-2试题</t>
-  </si>
-  <si>
-    <t>语文为新高考二卷,历史、政治为新高考卷,其他科目为全国甲卷</t>
-  </si>
-  <si>
-    <t>语文、数学、英语为新高考二卷,其他科目为甘肃卷</t>
   </si>
   <si>
     <t>新高考一二卷,全国甲卷,北京卷,天津卷,上海春秋考卷</t>
@@ -320,6 +314,18 @@
   </si>
   <si>
     <t>英语听力不计入总成绩,笔试按阅读和七选五每题2.5'→3',完形1'→2',语法填空1.5'→2'折算为总成绩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>语文、数学、英语为新高考二卷,其他科目为甘肃卷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>语文为新高考二卷,文综为西藏卷,其他科目为全国甲卷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>文综历史,政治部分是新高考卷,地理部分是全国甲卷</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -834,7 +840,7 @@
         <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -848,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -862,7 +868,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -898,7 +904,7 @@
         <v>66</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -912,7 +918,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -964,7 +970,7 @@
         <v>14</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -1010,7 +1016,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1197,9 +1203,11 @@
         <v>34</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="1"/>
+        <v>94</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
@@ -1221,7 +1229,7 @@
         <v>36</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D34" s="1"/>
     </row>
@@ -1260,7 +1268,7 @@
         <v>66</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -1289,7 +1297,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -1300,7 +1308,7 @@
         <v>8</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -1311,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
@@ -1322,7 +1330,7 @@
         <v>22</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
@@ -1333,7 +1341,7 @@
         <v>22</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
@@ -1344,7 +1352,7 @@
         <v>22</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
@@ -1355,7 +1363,7 @@
         <v>22</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
@@ -1366,7 +1374,7 @@
         <v>22</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="42.75" x14ac:dyDescent="0.2">
@@ -1377,7 +1385,7 @@
         <v>22</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
